--- a/exemples_risk_intelligence/ECOBANK_Data_Export_2026-09-30.xlsx
+++ b/exemples_risk_intelligence/ECOBANK_Data_Export_2026-09-30.xlsx
@@ -510,7 +510,7 @@
       </c>
       <c r="T5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Escalade contentieux</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="T8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="T16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Promesse de règlement</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="T28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Promesse de règlement</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="T31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Promesse de règlement</t>
         </is>
       </c>
     </row>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="T34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Promesse de règlement</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="T40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">En cours</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="T65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="T71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">En cours</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="T72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="T81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Promesse de règlement</t>
         </is>
       </c>
     </row>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="T85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Promesse de règlement</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="T97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="T135" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -11852,7 +11852,7 @@
       </c>
       <c r="T152" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Escalade contentieux</t>
         </is>
       </c>
     </row>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="T158" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="T159" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="T160" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Promesse de règlement</t>
         </is>
       </c>
     </row>
@@ -13462,7 +13462,7 @@
       </c>
       <c r="T173" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>

--- a/exemples_risk_intelligence/ECOBANK_Data_Export_2026-09-30.xlsx
+++ b/exemples_risk_intelligence/ECOBANK_Data_Export_2026-09-30.xlsx
@@ -159,7 +159,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECOBANK SÉNÉGAL · CREDIT RISK INTELLIGENCE · DATA EXPORT · arrêté 30/09/2026 · source : M_09.xlsx</t>
+          <t xml:space="preserve">ECOBANK SÉNÉGAL · CREDIT RISK INTELLIGENCE · DATA EXPORT · arrêté 30/09/2026 · source : N_09.xlsx</t>
         </is>
       </c>
       <c r="B1" s="1"/>
@@ -292,7 +292,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOCIETE 0378</t>
+          <t xml:space="preserve">BAOBAB NEGOCE SA</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -366,7 +366,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOCIETE 0388</t>
+          <t xml:space="preserve">KORA TRANSPORTS ET FILS</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -440,7 +440,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOCIETE 0353</t>
+          <t xml:space="preserve">SAHEL CIMENTS INDUSTRIE SA</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOCIETE 0483</t>
+          <t xml:space="preserve">TERANGA BATIMENT TRAVAUX PUBLICS</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOCIETE 0370</t>
+          <t xml:space="preserve">KORA LOGISTIQUE ET TRANSIT</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOCIETE 0355</t>
+          <t xml:space="preserve">BAOBAB NEGOCE DISTRIBUTION SARL</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOCIETE 0461</t>
+          <t xml:space="preserve">SAHEL PECHE ARMEMENT</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOCIETE 0561</t>
+          <t xml:space="preserve">NIAYES HORTICULTURE EXPORT</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOCIETE 0454</t>
+          <t xml:space="preserve">TERANGA IMMOBILIER PROMOTION</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOCIETE 0364</t>
+          <t xml:space="preserve">COOPERATIVE AGRICOLE DES NIAYES</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="T16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Promesse de règlement</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="T28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Promesse de règlement</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="T34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Promesse de règlement</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="T40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">En cours</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="T59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="T65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Revue analyste</t>
+          <t xml:space="preserve">Promesse de règlement</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="T68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">En cours</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="T72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Revue analyste</t>
+          <t xml:space="preserve">En cours</t>
         </is>
       </c>
     </row>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="T85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Promesse de règlement</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -7672,7 +7672,7 @@
       </c>
       <c r="T98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="T158" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Revue analyste</t>
+          <t xml:space="preserve">Restructuration</t>
         </is>
       </c>
     </row>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="T175" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -19606,7 +19606,7 @@
       </c>
       <c r="T253" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
